--- a/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
+++ b/ReDiv_Online/ExcelTool/LubanTools/DataTables/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\RAFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\REDIV\ReDiv_Online\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7B62D3-A21B-4DF0-9D50-3B0BC24F932C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F6233F3-9E4A-4523-B07B-FF2569364C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2030" yWindow="1040" windowWidth="44100" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="5910" windowWidth="44100" windowHeight="14560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -99,30 +99,6 @@
   </si>
   <si>
     <t>字段变体</t>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>表</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>多语言表</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>多语言Key</t>
   </si>
 </sst>
 </file>
@@ -207,7 +183,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -219,9 +195,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -509,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="26.4140625" customWidth="1"/>
@@ -551,15 +524,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -617,48 +590,17 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="1">
